--- a/从零开始学Slots/从零开始学Slots-05-数值篇-3x3LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-05-数值篇-3x3LineSlots.xlsx
@@ -7040,6 +7040,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M161" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8458,5 +8461,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P116" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-05-数值篇-3x3LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-05-数值篇-3x3LineSlots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="194">
   <si>
     <r>
       <rPr>
@@ -5977,7 +5977,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6124,6 +6124,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7101,8 +7113,8 @@
       <c r="B5" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>116</v>
+      <c r="C5" s="37">
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7133,8 +7145,8 @@
       <c r="B8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>121</v>
+      <c r="C8" s="38">
+        <v>3</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
@@ -7684,8 +7696,8 @@
       <c r="A50" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B50" s="21" t="s">
-        <v>149</v>
+      <c r="B50" s="39">
+        <v>3</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>106</v>

--- a/从零开始学Slots/从零开始学Slots-05-数值篇-3x3LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-05-数值篇-3x3LineSlots.xlsx
@@ -5788,12 +5788,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -5977,7 +5978,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6136,6 +6137,14 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7870,7 +7879,7 @@
         <f aca="false">B62*C62*D62</f>
         <v>125</v>
       </c>
-      <c r="F62" s="24" t="n">
+      <c r="F62" s="40" t="n">
         <f aca="false">E62/$B$11</f>
         <v>0.00462962962962963</v>
       </c>
@@ -7903,7 +7912,7 @@
         <f aca="false">B63*C63*D63</f>
         <v>125</v>
       </c>
-      <c r="F63" s="24" t="n">
+      <c r="F63" s="40" t="n">
         <f aca="false">E63/$B$11</f>
         <v>0.00462962962962963</v>
       </c>
@@ -7936,7 +7945,7 @@
         <f aca="false">B64*C64*D64</f>
         <v>125</v>
       </c>
-      <c r="F64" s="24" t="n">
+      <c r="F64" s="40" t="n">
         <f aca="false">E64/$B$11</f>
         <v>0.00462962962962963</v>
       </c>
@@ -7969,7 +7978,7 @@
         <f aca="false">B65*C65*D65</f>
         <v>27</v>
       </c>
-      <c r="F65" s="24" t="n">
+      <c r="F65" s="40" t="n">
         <f aca="false">E65/$B$11</f>
         <v>0.001</v>
       </c>
@@ -8002,7 +8011,7 @@
         <f aca="false">B66*C66*D66</f>
         <v>27</v>
       </c>
-      <c r="F66" s="24" t="n">
+      <c r="F66" s="40" t="n">
         <f aca="false">E66/$B$11</f>
         <v>0.001</v>
       </c>
@@ -8035,7 +8044,7 @@
         <f aca="false">B67*C67*D67</f>
         <v>27</v>
       </c>
-      <c r="F67" s="24" t="n">
+      <c r="F67" s="40" t="n">
         <f aca="false">E67/$B$11</f>
         <v>0.001</v>
       </c>
@@ -8068,7 +8077,7 @@
         <f aca="false">B68*C68*D68</f>
         <v>27</v>
       </c>
-      <c r="F68" s="24" t="n">
+      <c r="F68" s="40" t="n">
         <f aca="false">E68/$B$11</f>
         <v>0.001</v>
       </c>
@@ -8101,7 +8110,7 @@
         <f aca="false">B69*C69*D69</f>
         <v>27</v>
       </c>
-      <c r="F69" s="24" t="n">
+      <c r="F69" s="40" t="n">
         <f aca="false">E69/$B$11</f>
         <v>0.001</v>
       </c>
